--- a/BWI/bestwine_output/bestwine_South Korea.xlsx
+++ b/BWI/bestwine_output/bestwine_South Korea.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA159"/>
+  <dimension ref="A1:AA160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17131,6 +17131,95 @@
       <c r="Z159" s="2" t="inlineStr"/>
       <c r="AA159" s="2" t="inlineStr"/>
     </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>All Vintage Wine Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>All Vintage Wine Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>34799</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Seocho-gu</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Seoul</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>4, Hyeongchon 3-gil, Seocho-gu</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>06765</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.allvintage.co.kr</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>david@allvintage.co.kr</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>+82 2-586-2098</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>2148829564</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="inlineStr"/>
+      <c r="S160" s="2" t="inlineStr"/>
+      <c r="T160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/allvin_wine</t>
+        </is>
+      </c>
+      <c r="U160" s="2" t="inlineStr"/>
+      <c r="V160" s="2" t="inlineStr"/>
+      <c r="W160" s="2" t="inlineStr"/>
+      <c r="X160" s="2" t="inlineStr"/>
+      <c r="Y160" s="2" t="inlineStr"/>
+      <c r="Z160" s="2" t="inlineStr"/>
+      <c r="AA160" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Korea.xlsx
+++ b/BWI/bestwine_output/bestwine_South Korea.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA160"/>
+  <dimension ref="A1:AA161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17220,6 +17220,95 @@
       <c r="Z160" s="2" t="inlineStr"/>
       <c r="AA160" s="2" t="inlineStr"/>
     </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>All Vintage Wine Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>All Vintage Wine Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>34799</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Seocho-gu</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Seoul</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>4, Hyeongchon 3-gil, Seocho-gu</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>06765</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.allvintage.co.kr</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr"/>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>david@allvintage.co.kr</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>+82 2-586-2098</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>2148829564</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="inlineStr"/>
+      <c r="S161" s="2" t="inlineStr"/>
+      <c r="T161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/allvin_wine</t>
+        </is>
+      </c>
+      <c r="U161" s="2" t="inlineStr"/>
+      <c r="V161" s="2" t="inlineStr"/>
+      <c r="W161" s="2" t="inlineStr"/>
+      <c r="X161" s="2" t="inlineStr"/>
+      <c r="Y161" s="2" t="inlineStr"/>
+      <c r="Z161" s="2" t="inlineStr"/>
+      <c r="AA161" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Korea.xlsx
+++ b/BWI/bestwine_output/bestwine_South Korea.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA161"/>
+  <dimension ref="A1:AA162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17309,6 +17309,95 @@
       <c r="Z161" s="2" t="inlineStr"/>
       <c r="AA161" s="2" t="inlineStr"/>
     </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>All Vintage Wine Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>All Vintage Wine Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>34799</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Seocho-gu</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Seoul</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>4, Hyeongchon 3-gil, Seocho-gu</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>06765</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.allvintage.co.kr</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>david@allvintage.co.kr</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>+82 2-586-2098</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>2148829564</t>
+        </is>
+      </c>
+      <c r="R162" s="2" t="inlineStr"/>
+      <c r="S162" s="2" t="inlineStr"/>
+      <c r="T162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/allvin_wine</t>
+        </is>
+      </c>
+      <c r="U162" s="2" t="inlineStr"/>
+      <c r="V162" s="2" t="inlineStr"/>
+      <c r="W162" s="2" t="inlineStr"/>
+      <c r="X162" s="2" t="inlineStr"/>
+      <c r="Y162" s="2" t="inlineStr"/>
+      <c r="Z162" s="2" t="inlineStr"/>
+      <c r="AA162" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
